--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.63263661875935</v>
+        <v>2.215303450548395</v>
       </c>
       <c r="D2" t="n">
-        <v>14.14698341913553</v>
+        <v>2.298884805609524</v>
       </c>
       <c r="E2" t="n">
-        <v>3.847820084916812</v>
+        <v>0.6252707637989819</v>
       </c>
       <c r="F2" t="n">
-        <v>8.931890247349234</v>
+        <v>1.451432165194251</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.79281088238865</v>
+        <v>2.566331768388156</v>
       </c>
       <c r="D3" t="n">
-        <v>32.83313894096941</v>
+        <v>5.335385077907529</v>
       </c>
       <c r="E3" t="n">
-        <v>3.847820084916812</v>
+        <v>0.6252707637989819</v>
       </c>
       <c r="F3" t="n">
-        <v>8.931890247349234</v>
+        <v>1.451432165194251</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.65790925435972</v>
+        <v>3.681910253833454</v>
       </c>
       <c r="D4" t="n">
-        <v>13.63487578765656</v>
+        <v>2.215667315494191</v>
       </c>
       <c r="E4" t="n">
-        <v>3.847820084916812</v>
+        <v>0.6252707637989819</v>
       </c>
       <c r="F4" t="n">
-        <v>8.931890247349234</v>
+        <v>1.451432165194251</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
